--- a/5/search/FY5_Missile2_results/solutions_direction_117.0.xlsx
+++ b/5/search/FY5_Missile2_results/solutions_direction_117.0.xlsx
@@ -490,7 +490,7 @@
         <v>117</v>
       </c>
       <c r="B2" t="n">
-        <v>134.4</v>
+        <v>134</v>
       </c>
       <c r="C2" t="n">
         <v>20</v>
@@ -499,25 +499,25 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>11779.6735367001</v>
+        <v>11783.30546069801</v>
       </c>
       <c r="F2" t="n">
-        <v>395.0255370183327</v>
+        <v>387.8974848248258</v>
       </c>
       <c r="G2" t="n">
         <v>1300</v>
       </c>
       <c r="H2" t="n">
-        <v>11779.6735367001</v>
+        <v>11783.30546069801</v>
       </c>
       <c r="I2" t="n">
-        <v>395.0255370183327</v>
+        <v>387.8974848248258</v>
       </c>
       <c r="J2" t="n">
         <v>1300</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
